--- a/EPFU_2025/EPFU_Interpolated_Weights.xlsx
+++ b/EPFU_2025/EPFU_Interpolated_Weights.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Ashlyn_thesis\EPFU_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65403D86-DD6B-4C8C-A1B1-0FD137610851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AAFA8F-03D2-4583-A0B4-94FDB8ABDB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3490" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3432" uniqueCount="93">
   <si>
     <t>Bat_ID</t>
   </si>
@@ -16210,7 +16210,7 @@
     </row>
     <row r="425" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B425" s="6">
         <v>30.6</v>
@@ -17771,13 +17771,9 @@
       <c r="AG466" s="3"/>
     </row>
     <row r="467" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A467" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A467" s="3"/>
       <c r="B467" s="3"/>
-      <c r="C467" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="C467" s="3"/>
       <c r="G467" s="17"/>
       <c r="H467" s="3"/>
       <c r="I467" s="3"/>
@@ -19319,13 +19315,9 @@
       <c r="AG509" s="3"/>
     </row>
     <row r="510" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A510" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A510" s="3"/>
       <c r="B510" s="3"/>
-      <c r="C510" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="C510" s="3"/>
       <c r="G510" s="17"/>
       <c r="H510" s="3"/>
       <c r="I510" s="3"/>
@@ -20867,13 +20859,9 @@
       <c r="AG552" s="3"/>
     </row>
     <row r="553" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A553" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A553" s="3"/>
       <c r="B553" s="3"/>
-      <c r="C553" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="C553" s="3"/>
       <c r="G553" s="17"/>
       <c r="H553" s="3"/>
       <c r="I553" s="3"/>
@@ -22415,13 +22403,9 @@
       <c r="AG595" s="3"/>
     </row>
     <row r="596" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A596" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A596" s="3"/>
       <c r="B596" s="3"/>
-      <c r="C596" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="C596" s="3"/>
       <c r="G596" s="17"/>
       <c r="H596" s="3"/>
       <c r="I596" s="3"/>
@@ -23963,13 +23947,9 @@
       <c r="AG638" s="3"/>
     </row>
     <row r="639" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A639" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A639" s="3"/>
       <c r="B639" s="3"/>
-      <c r="C639" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="C639" s="3"/>
       <c r="G639" s="17"/>
       <c r="H639" s="3"/>
       <c r="I639" s="3"/>
@@ -25511,13 +25491,9 @@
       <c r="AG681" s="3"/>
     </row>
     <row r="682" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A682" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A682" s="3"/>
       <c r="B682" s="3"/>
-      <c r="C682" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="C682" s="3"/>
       <c r="G682" s="17"/>
       <c r="H682" s="3"/>
       <c r="I682" s="3"/>
@@ -27059,13 +27035,9 @@
       <c r="AG724" s="3"/>
     </row>
     <row r="725" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A725" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A725" s="3"/>
       <c r="B725" s="3"/>
-      <c r="C725" s="3" t="s">
-        <v>65</v>
-      </c>
+      <c r="C725" s="3"/>
       <c r="G725" s="17"/>
       <c r="H725" s="3"/>
       <c r="I725" s="3"/>
@@ -28607,13 +28579,9 @@
       <c r="AG767" s="3"/>
     </row>
     <row r="768" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A768" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A768" s="3"/>
       <c r="B768" s="3"/>
-      <c r="C768" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="C768" s="3"/>
       <c r="G768" s="17"/>
       <c r="H768" s="3"/>
       <c r="I768" s="3"/>
@@ -30155,13 +30123,9 @@
       <c r="AG810" s="3"/>
     </row>
     <row r="811" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A811" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A811" s="3"/>
       <c r="B811" s="3"/>
-      <c r="C811" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="C811" s="3"/>
       <c r="G811" s="17"/>
       <c r="H811" s="3"/>
       <c r="I811" s="3"/>
@@ -31703,13 +31667,9 @@
       <c r="AG853" s="3"/>
     </row>
     <row r="854" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A854" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A854" s="3"/>
       <c r="B854" s="3"/>
-      <c r="C854" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="C854" s="3"/>
       <c r="G854" s="17"/>
       <c r="H854" s="3"/>
       <c r="I854" s="3"/>
@@ -33251,13 +33211,9 @@
       <c r="AG896" s="3"/>
     </row>
     <row r="897" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A897" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A897" s="3"/>
       <c r="B897" s="3"/>
-      <c r="C897" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="C897" s="3"/>
       <c r="G897" s="17"/>
       <c r="H897" s="3"/>
       <c r="I897" s="3"/>
@@ -34799,13 +34755,9 @@
       <c r="AG939" s="3"/>
     </row>
     <row r="940" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A940" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A940" s="3"/>
       <c r="B940" s="3"/>
-      <c r="C940" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="C940" s="3"/>
       <c r="G940" s="17"/>
       <c r="H940" s="3"/>
       <c r="I940" s="3"/>
@@ -36347,13 +36299,9 @@
       <c r="AG982" s="3"/>
     </row>
     <row r="983" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A983" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A983" s="3"/>
       <c r="B983" s="3"/>
-      <c r="C983" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="C983" s="3"/>
       <c r="G983" s="17"/>
       <c r="H983" s="3"/>
       <c r="I983" s="3"/>
@@ -37895,13 +37843,9 @@
       <c r="AG1025" s="3"/>
     </row>
     <row r="1026" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1026" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1026" s="3"/>
       <c r="B1026" s="3"/>
-      <c r="C1026" s="3" t="s">
-        <v>72</v>
-      </c>
+      <c r="C1026" s="3"/>
       <c r="G1026" s="17"/>
       <c r="H1026" s="3"/>
       <c r="I1026" s="3"/>
@@ -39443,13 +39387,9 @@
       <c r="AG1068" s="3"/>
     </row>
     <row r="1069" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1069" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1069" s="3"/>
       <c r="B1069" s="3"/>
-      <c r="C1069" s="3" t="s">
-        <v>73</v>
-      </c>
+      <c r="C1069" s="3"/>
       <c r="G1069" s="17"/>
       <c r="H1069" s="3"/>
       <c r="I1069" s="3"/>
@@ -40991,13 +40931,9 @@
       <c r="AG1111" s="3"/>
     </row>
     <row r="1112" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1112" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1112" s="3"/>
       <c r="B1112" s="3"/>
-      <c r="C1112" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="C1112" s="3"/>
       <c r="G1112" s="17"/>
       <c r="H1112" s="3"/>
       <c r="I1112" s="3"/>
@@ -42539,13 +42475,9 @@
       <c r="AG1154" s="3"/>
     </row>
     <row r="1155" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1155" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1155" s="3"/>
       <c r="B1155" s="3"/>
-      <c r="C1155" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="C1155" s="3"/>
       <c r="G1155" s="17"/>
       <c r="H1155" s="3"/>
       <c r="I1155" s="3"/>
@@ -44087,13 +44019,9 @@
       <c r="AG1197" s="3"/>
     </row>
     <row r="1198" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1198" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1198" s="3"/>
       <c r="B1198" s="3"/>
-      <c r="C1198" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="C1198" s="3"/>
       <c r="G1198" s="17"/>
       <c r="H1198" s="3"/>
       <c r="I1198" s="3"/>
@@ -45635,13 +45563,9 @@
       <c r="AG1240" s="3"/>
     </row>
     <row r="1241" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1241" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1241" s="3"/>
       <c r="B1241" s="3"/>
-      <c r="C1241" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="C1241" s="3"/>
       <c r="G1241" s="17"/>
       <c r="H1241" s="3"/>
       <c r="I1241" s="3"/>
@@ -47183,13 +47107,9 @@
       <c r="AG1283" s="3"/>
     </row>
     <row r="1284" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1284" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1284" s="3"/>
       <c r="B1284" s="3"/>
-      <c r="C1284" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="C1284" s="3"/>
       <c r="G1284" s="17"/>
       <c r="H1284" s="3"/>
       <c r="I1284" s="3"/>
@@ -48731,13 +48651,9 @@
       <c r="AG1326" s="3"/>
     </row>
     <row r="1327" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1327" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1327" s="3"/>
       <c r="B1327" s="3"/>
-      <c r="C1327" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="C1327" s="3"/>
       <c r="G1327" s="17"/>
       <c r="H1327" s="3"/>
       <c r="I1327" s="3"/>
@@ -50279,13 +50195,9 @@
       <c r="AG1369" s="3"/>
     </row>
     <row r="1370" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1370" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1370" s="3"/>
       <c r="B1370" s="3"/>
-      <c r="C1370" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="C1370" s="3"/>
       <c r="G1370" s="17"/>
       <c r="H1370" s="3"/>
       <c r="I1370" s="3"/>
@@ -51827,13 +51739,9 @@
       <c r="AG1412" s="3"/>
     </row>
     <row r="1413" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1413" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1413" s="3"/>
       <c r="B1413" s="3"/>
-      <c r="C1413" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="C1413" s="3"/>
       <c r="G1413" s="17"/>
       <c r="H1413" s="3"/>
       <c r="I1413" s="3"/>
@@ -53375,13 +53283,9 @@
       <c r="AG1455" s="3"/>
     </row>
     <row r="1456" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1456" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1456" s="3"/>
       <c r="B1456" s="3"/>
-      <c r="C1456" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="C1456" s="3"/>
       <c r="G1456" s="17"/>
       <c r="H1456" s="3"/>
       <c r="I1456" s="3"/>
@@ -54923,13 +54827,9 @@
       <c r="AG1498" s="3"/>
     </row>
     <row r="1499" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1499" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1499" s="3"/>
       <c r="B1499" s="3"/>
-      <c r="C1499" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="C1499" s="3"/>
       <c r="G1499" s="17"/>
       <c r="H1499" s="3"/>
       <c r="I1499" s="3"/>
@@ -56471,13 +56371,9 @@
       <c r="AG1541" s="3"/>
     </row>
     <row r="1542" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1542" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1542" s="3"/>
       <c r="B1542" s="3"/>
-      <c r="C1542" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="C1542" s="3"/>
       <c r="G1542" s="17"/>
       <c r="H1542" s="3"/>
       <c r="I1542" s="3"/>
@@ -58019,13 +57915,9 @@
       <c r="AG1584" s="3"/>
     </row>
     <row r="1585" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1585" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1585" s="3"/>
       <c r="B1585" s="3"/>
-      <c r="C1585" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="C1585" s="3"/>
       <c r="G1585" s="17"/>
       <c r="H1585" s="3"/>
       <c r="I1585" s="3"/>
@@ -59599,13 +59491,9 @@
       <c r="AG1627" s="3"/>
     </row>
     <row r="1628" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1628" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1628" s="3"/>
       <c r="B1628" s="3"/>
-      <c r="C1628" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="C1628" s="3"/>
       <c r="D1628" s="3"/>
       <c r="E1628" s="3"/>
       <c r="F1628" s="18"/>
@@ -61276,13 +61164,9 @@
       <c r="AG1670" s="3"/>
     </row>
     <row r="1671" spans="1:33" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1671" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1671" s="3"/>
       <c r="B1671" s="3"/>
-      <c r="C1671" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="C1671" s="3"/>
       <c r="D1671" s="3"/>
       <c r="E1671" s="3"/>
       <c r="F1671" s="18"/>
